--- a/data/players/Will_Goodwin_master.xlsx
+++ b/data/players/Will_Goodwin_master.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Physical" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Pressing" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Off_Ball_Runs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Match_by_Match" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Wyscout" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Merged" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Physical" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pressing" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Off_Ball_Runs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Match_by_Match" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wyscout" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Merged" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -60,11 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -763,12 +767,9 @@
       <c r="AH2" t="n">
         <v>1.1</v>
       </c>
-      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
         <v>34</v>
       </c>
@@ -902,17 +903,12 @@
       <c r="AH3" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
         <v>7</v>
       </c>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1034,13 +1030,9 @@
       <c r="AG4" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
         <v>22</v>
       </c>
@@ -1174,14 +1166,12 @@
       <c r="AH5" t="n">
         <v>0.63</v>
       </c>
-      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
         <v>1</v>
       </c>
       <c r="AK5" t="n">
         <v>2.62</v>
       </c>
-      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
         <v>14</v>
       </c>
@@ -1312,20 +1302,15 @@
       <c r="AG6" t="n">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="n">
         <v>5</v>
       </c>
       <c r="AN6" t="n">
         <v>2.2</v>
       </c>
-      <c r="AO6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1447,18 +1432,12 @@
       <c r="AG7" t="n">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
       <c r="AM7" t="n">
         <v>3</v>
       </c>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1580,20 +1559,15 @@
       <c r="AG8" t="n">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
       <c r="AM8" t="n">
         <v>11</v>
       </c>
       <c r="AN8" t="n">
         <v>2.04</v>
       </c>
-      <c r="AO8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1718,17 +1692,12 @@
       <c r="AH9" t="n">
         <v>0.93</v>
       </c>
-      <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
       <c r="AM9" t="n">
         <v>7</v>
       </c>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1853,18 +1822,15 @@
       <c r="AH10" t="n">
         <v>0.87</v>
       </c>
-      <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="n">
         <v>1</v>
       </c>
       <c r="AK10" t="n">
         <v>2.07</v>
       </c>
-      <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="n">
         <v>6</v>
       </c>
-      <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="n">
         <v>3.08</v>
       </c>
@@ -2001,7 +1967,6 @@
       <c r="AK11" t="n">
         <v>1.84</v>
       </c>
-      <c r="AL11" t="inlineStr"/>
       <c r="AM11" t="n">
         <v>37</v>
       </c>
@@ -2135,21 +2100,18 @@
       <c r="AH12" t="n">
         <v>0.71</v>
       </c>
-      <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="n">
         <v>1</v>
       </c>
       <c r="AK12" t="n">
         <v>1.33</v>
       </c>
-      <c r="AL12" t="inlineStr"/>
       <c r="AM12" t="n">
         <v>20</v>
       </c>
       <c r="AN12" t="n">
         <v>2.2</v>
       </c>
-      <c r="AO12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2280,15 +2242,12 @@
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
       <c r="AM13" t="n">
         <v>49</v>
       </c>
       <c r="AN13" t="n">
         <v>2.18</v>
       </c>
-      <c r="AO13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2422,7 +2381,6 @@
       <c r="AK14" t="n">
         <v>1.6</v>
       </c>
-      <c r="AL14" t="inlineStr"/>
       <c r="AM14" t="n">
         <v>25</v>
       </c>
@@ -2556,14 +2514,12 @@
       <c r="AH15" t="n">
         <v>0.82</v>
       </c>
-      <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="n">
         <v>1</v>
       </c>
       <c r="AK15" t="n">
         <v>1.34</v>
       </c>
-      <c r="AL15" t="inlineStr"/>
       <c r="AM15" t="n">
         <v>44</v>
       </c>
@@ -2703,8 +2659,6 @@
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
       <c r="AM16" t="n">
         <v>57</v>
       </c>
@@ -2838,17 +2792,12 @@
       <c r="AH17" t="n">
         <v>0.71</v>
       </c>
-      <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
       <c r="AM17" t="n">
         <v>10</v>
       </c>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2973,21 +2922,18 @@
       <c r="AH18" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="n">
         <v>2</v>
       </c>
       <c r="AK18" t="n">
         <v>1.42</v>
       </c>
-      <c r="AL18" t="inlineStr"/>
       <c r="AM18" t="n">
         <v>23</v>
       </c>
       <c r="AN18" t="n">
         <v>1.99</v>
       </c>
-      <c r="AO18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3121,14 +3067,12 @@
       <c r="AK19" t="n">
         <v>1.68</v>
       </c>
-      <c r="AL19" t="inlineStr"/>
       <c r="AM19" t="n">
         <v>15</v>
       </c>
       <c r="AN19" t="n">
         <v>2.01</v>
       </c>
-      <c r="AO19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3259,8 +3203,6 @@
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="n">
         <v>11</v>
       </c>
@@ -3585,7 +3527,6 @@
       <c r="AB2" t="n">
         <v>100</v>
       </c>
-      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
@@ -3598,14 +3539,12 @@
       <c r="AG2" t="n">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
-      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3735,7 +3674,6 @@
       <c r="AG3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
         <v>3</v>
       </c>
@@ -3874,7 +3812,6 @@
       <c r="AG4" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
         <v>1</v>
       </c>
@@ -3995,8 +3932,6 @@
       <c r="AA5" t="n">
         <v>0</v>
       </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
@@ -4009,14 +3944,12 @@
       <c r="AG5" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
-      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4269,8 +4202,6 @@
       <c r="AA7" t="n">
         <v>0</v>
       </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
@@ -4283,14 +4214,12 @@
       <c r="AG7" t="n">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
-      <c r="AK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4570,7 +4499,6 @@
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
-      <c r="AK9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4682,8 +4610,6 @@
       <c r="AA10" t="n">
         <v>0</v>
       </c>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
@@ -4696,14 +4622,12 @@
       <c r="AG10" t="n">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
-      <c r="AK10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5115,7 +5039,6 @@
       <c r="AG13" t="n">
         <v>0</v>
       </c>
-      <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="n">
         <v>1</v>
       </c>
@@ -5254,14 +5177,12 @@
       <c r="AG14" t="n">
         <v>0</v>
       </c>
-      <c r="AH14" t="inlineStr"/>
       <c r="AI14" t="n">
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
-      <c r="AK14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8318,18 +8239,12 @@
       <c r="AA2" t="n">
         <v>3</v>
       </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
         <v>34</v>
       </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8421,18 +8336,12 @@
       <c r="AA3" t="n">
         <v>1</v>
       </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
         <v>7</v>
       </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8524,18 +8433,12 @@
       <c r="AA4" t="n">
         <v>0</v>
       </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
         <v>22</v>
       </c>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8627,18 +8530,12 @@
       <c r="AA5" t="n">
         <v>1</v>
       </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
         <v>1</v>
       </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
         <v>14</v>
       </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8730,18 +8627,12 @@
       <c r="AA6" t="n">
         <v>0</v>
       </c>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
         <v>5</v>
       </c>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8833,18 +8724,12 @@
       <c r="AA7" t="n">
         <v>0</v>
       </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
         <v>3</v>
       </c>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8936,18 +8821,12 @@
       <c r="AA8" t="n">
         <v>0</v>
       </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="n">
         <v>11</v>
       </c>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9039,18 +8918,12 @@
       <c r="AA9" t="n">
         <v>3</v>
       </c>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
         <v>7</v>
       </c>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9142,18 +9015,12 @@
       <c r="AA10" t="n">
         <v>2</v>
       </c>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
         <v>1</v>
       </c>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
         <v>6</v>
       </c>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9245,18 +9112,12 @@
       <c r="AA11" t="n">
         <v>6</v>
       </c>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
         <v>3</v>
       </c>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="n">
         <v>37</v>
       </c>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9348,18 +9209,12 @@
       <c r="AA12" t="n">
         <v>1</v>
       </c>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="n">
         <v>1</v>
       </c>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="n">
         <v>20</v>
       </c>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9451,18 +9306,12 @@
       <c r="AA13" t="n">
         <v>2</v>
       </c>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="n">
         <v>49</v>
       </c>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9554,18 +9403,12 @@
       <c r="AA14" t="n">
         <v>5</v>
       </c>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="n">
         <v>25</v>
       </c>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9657,18 +9500,12 @@
       <c r="AA15" t="n">
         <v>4</v>
       </c>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="n">
         <v>1</v>
       </c>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="n">
         <v>44</v>
       </c>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9760,18 +9597,12 @@
       <c r="AA16" t="n">
         <v>4</v>
       </c>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="n">
         <v>57</v>
       </c>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9863,18 +9694,12 @@
       <c r="AA17" t="n">
         <v>2</v>
       </c>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="n">
         <v>0</v>
       </c>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="n">
         <v>10</v>
       </c>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9909,37 +9734,12 @@
       <c r="H18" t="n">
         <v>1214</v>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10031,18 +9831,12 @@
       <c r="AA19" t="n">
         <v>3</v>
       </c>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="n">
         <v>2</v>
       </c>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="n">
         <v>23</v>
       </c>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10077,37 +9871,12 @@
       <c r="H20" t="n">
         <v>1214</v>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10199,18 +9968,12 @@
       <c r="AA21" t="n">
         <v>4</v>
       </c>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="n">
         <v>2</v>
       </c>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
         <v>15</v>
       </c>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10302,18 +10065,12 @@
       <c r="AA22" t="n">
         <v>1</v>
       </c>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="n">
         <v>0</v>
       </c>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="n">
         <v>11</v>
       </c>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10326,366 +10083,366 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT20"/>
+  <dimension ref="A1:BT25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Match</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Minutes played</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Total actions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>successful</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Goals</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Assists</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Shots</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>on target</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>xG</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Passes</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>accurate</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Long passes</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>accurate</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>accurate.1</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Crosses</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>accurate</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>accurate.2</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>Dribbles</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>successful</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>successful.1</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>Duels</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>won</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Aerial duels</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>won</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>won.1</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Interceptions</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Losses</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>own half</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Recoveries</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>opp. half</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Yellow card</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Red card</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Defensive duels</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>won</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>won.2</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Loose ball duels</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>won</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>won.3</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Sliding tackles</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>successful</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>successful.2</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Clearances</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Fouls</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Yellow cards</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Red cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Shot assists</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Offensive duels</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>won</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>won.4</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Touches in penalty area</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Offsides</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Progressive runs</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Fouls suffered</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Through passes</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>accurate</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>accurate.3</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
         <is>
           <t>xA</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Second assists</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>Passes to final third</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>accurate</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>accurate.4</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
         <is>
           <t>Passes to penalty area</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>accurate</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>accurate.5</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
         <is>
           <t>Received passes</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>Forward passes</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>accurate</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>accurate.6</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
         <is>
           <t>Back passes</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>accurate</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>accurate.7</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>Conceded goals</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>xCG</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>Shots against</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>Saves</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>with reflexes</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>Exits</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>Passes to GK</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
-        <is>
-          <t>accurate</t>
-        </is>
-      </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>accurate.8</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
         <is>
           <t>Goal kicks</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>Short goal kicks</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>Long goal kicks</t>
         </is>
@@ -10694,7 +10451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colchester United - Barnet 4:1</t>
+          <t>Bromley - Colchester United 1:0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -10702,10 +10459,8 @@
           <t>England. League Two</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-02-21</t>
-        </is>
+      <c r="C2" s="2" t="n">
+        <v>46102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -10713,13 +10468,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -10728,97 +10483,81 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>13</v>
-      </c>
-      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="n">
         <v>11</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>18</v>
-      </c>
       <c r="V2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA2" t="n">
         <v>4</v>
       </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
       <c r="AB2" t="n">
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -10827,16 +10566,16 @@
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
@@ -10847,42 +10586,30 @@
       <c r="AW2" t="n">
         <v>0</v>
       </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BF2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BI2" t="inlineStr"/>
       <c r="BJ2" t="n">
         <v>0</v>
       </c>
@@ -10892,21 +10619,13 @@
       <c r="BL2" t="n">
         <v>0</v>
       </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
       <c r="BO2" t="n">
         <v>0</v>
       </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
       <c r="BR2" t="n">
         <v>0</v>
       </c>
@@ -10920,7 +10639,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cambridge United - Colchester United 1:1</t>
+          <t>Milton Keynes Dons - Colchester United 1:0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10928,10 +10647,8 @@
           <t>England. League Two</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
+      <c r="C3" s="2" t="n">
+        <v>46099</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -10939,176 +10656,148 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F3" t="n">
         <v>16</v>
       </c>
       <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W3" t="n">
+        <v>6</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
         <v>4</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="n">
         <v>5</v>
       </c>
-      <c r="AA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>2</v>
-      </c>
       <c r="BF3" t="n">
         <v>1</v>
       </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
+      <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="n">
         <v>0</v>
       </c>
@@ -11118,21 +10807,13 @@
       <c r="BL3" t="n">
         <v>0</v>
       </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="n">
         <v>0</v>
       </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
       <c r="BR3" t="n">
         <v>0</v>
       </c>
@@ -11146,7 +10827,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Barrow - Colchester United 1:0</t>
+          <t>Colchester United - Crawley Town 0:0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -11154,10 +10835,8 @@
           <t>England. League Two</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
+      <c r="C4" s="2" t="n">
+        <v>46094</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -11165,13 +10844,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>78</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -11180,61 +10859,53 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="M4" t="n">
-        <v>19</v>
-      </c>
-      <c r="N4" t="n">
-        <v>12</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>7</v>
+      </c>
+      <c r="V4" t="n">
         <v>3</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>15</v>
-      </c>
-      <c r="V4" t="n">
-        <v>8</v>
-      </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z4" t="n">
         <v>5</v>
       </c>
-      <c r="Z4" t="n">
-        <v>10</v>
-      </c>
       <c r="AA4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -11249,25 +10920,17 @@
         <v>1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -11276,65 +10939,53 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AT4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
       </c>
       <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="n">
         <v>3</v>
       </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>13</v>
-      </c>
       <c r="BF4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
@@ -11344,21 +10995,13 @@
       <c r="BL4" t="n">
         <v>0</v>
       </c>
-      <c r="BM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0</v>
-      </c>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="n">
         <v>0</v>
       </c>
-      <c r="BP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0</v>
-      </c>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
       <c r="BR4" t="n">
         <v>0</v>
       </c>
@@ -11372,7 +11015,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Colchester United - Shrewsbury Town 2:0</t>
+          <t>Newport County - Colchester United 1:2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -11380,84 +11023,72 @@
           <t>England. League Two</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CF</t>
-        </is>
+      <c r="C5" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>13</v>
-      </c>
-      <c r="N5" t="n">
-        <v>12</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -11475,25 +11106,17 @@
         <v>1</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
@@ -11505,13 +11128,13 @@
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
         <v>0</v>
@@ -11520,14 +11143,12 @@
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
@@ -11535,32 +11156,22 @@
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
       <c r="BE5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BI5" t="inlineStr"/>
       <c r="BJ5" t="n">
         <v>0</v>
       </c>
@@ -11570,21 +11181,13 @@
       <c r="BL5" t="n">
         <v>0</v>
       </c>
-      <c r="BM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>0</v>
-      </c>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="n">
         <v>0</v>
       </c>
-      <c r="BP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0</v>
-      </c>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
       <c r="BR5" t="n">
         <v>0</v>
       </c>
@@ -11598,7 +11201,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Crewe Alexandra - Colchester United 1:0</t>
+          <t>Colchester United - Salford City 0:1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -11606,10 +11209,8 @@
           <t>England. League Two</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-01-31</t>
-        </is>
+      <c r="C6" s="2" t="n">
+        <v>46081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -11617,13 +11218,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -11632,115 +11233,99 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>18</v>
-      </c>
-      <c r="N6" t="n">
         <v>9</v>
       </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>20</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>10</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y6" t="n">
         <v>3</v>
       </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>13</v>
-      </c>
-      <c r="V6" t="n">
-        <v>5</v>
-      </c>
-      <c r="W6" t="n">
+      <c r="Z6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>4</v>
       </c>
-      <c r="X6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>5</v>
-      </c>
       <c r="AR6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="n">
         <v>0</v>
@@ -11751,9 +11336,7 @@
       <c r="AW6" t="n">
         <v>0</v>
       </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
+      <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="n">
         <v>0</v>
       </c>
@@ -11761,32 +11344,22 @@
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
       <c r="BE6" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="BF6" t="n">
         <v>2</v>
       </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
+      <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="n">
         <v>0</v>
       </c>
@@ -11796,21 +11369,13 @@
       <c r="BL6" t="n">
         <v>0</v>
       </c>
-      <c r="BM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>0</v>
-      </c>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="n">
         <v>0</v>
       </c>
-      <c r="BP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>0</v>
-      </c>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
       <c r="BR6" t="n">
         <v>0</v>
       </c>
@@ -11824,7 +11389,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Colchester United - Grimsby Town 0:1</t>
+          <t>Colchester United - Barnet 4:1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -11832,10 +11397,8 @@
           <t>England. League Two</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-01-27</t>
-        </is>
+      <c r="C7" s="2" t="n">
+        <v>46074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -11843,13 +11406,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106</v>
+        <v>52</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -11858,82 +11421,82 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M7" t="n">
+        <v>13</v>
+      </c>
+      <c r="N7" t="n">
+        <v>11</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>18</v>
+      </c>
+      <c r="V7" t="n">
+        <v>6</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="M7" t="n">
-        <v>11</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>64</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
         <v>3</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AG7" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
-        <v>27</v>
-      </c>
-      <c r="V7" t="n">
-        <v>11</v>
-      </c>
-      <c r="W7" t="n">
-        <v>12</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
       <c r="AH7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -11942,13 +11505,13 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM7" t="n">
         <v>1</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -11960,55 +11523,55 @@
         <v>10</v>
       </c>
       <c r="AR7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AS7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
         <v>7</v>
       </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>10</v>
-      </c>
       <c r="BF7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BG7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BH7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BI7" t="n">
         <v>3</v>
@@ -12050,7 +11613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Colchester United - Fleetwood Town 2:1</t>
+          <t>Cambridge United - Colchester United 1:1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -12058,10 +11621,8 @@
           <t>England. League Two</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-01-24</t>
-        </is>
+      <c r="C8" s="2" t="n">
+        <v>46070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -12069,13 +11630,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -12093,19 +11654,19 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -12114,52 +11675,52 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA8" t="n">
         <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
         <v>1</v>
       </c>
       <c r="AD8" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -12168,13 +11729,13 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -12183,22 +11744,22 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
         <v>1</v>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -12213,7 +11774,7 @@
         <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB8" t="n">
         <v>0</v>
@@ -12225,7 +11786,7 @@
         <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BF8" t="n">
         <v>1</v>
@@ -12234,10 +11795,10 @@
         <v>0</v>
       </c>
       <c r="BH8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ8" t="n">
         <v>0</v>
@@ -12276,7 +11837,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Colchester United - Milton Keynes Dons 1:0</t>
+          <t>Barrow - Colchester United 1:0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -12284,10 +11845,8 @@
           <t>England. League Two</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
+      <c r="C9" s="2" t="n">
+        <v>46067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -12295,13 +11854,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12310,20 +11869,20 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
+        <v>19</v>
+      </c>
+      <c r="N9" t="n">
         <v>12</v>
       </c>
-      <c r="N9" t="n">
-        <v>7</v>
-      </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
@@ -12331,13 +11890,13 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -12346,124 +11905,124 @@
         <v>15</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS9" t="n">
         <v>4</v>
       </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="AT9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI9" t="n">
         <v>4</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>1</v>
       </c>
       <c r="BJ9" t="n">
         <v>0</v>
@@ -12502,7 +12061,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gillingham - Colchester United 1:1</t>
+          <t>Colchester United - Shrewsbury Town 2:0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -12510,108 +12069,106 @@
           <t>England. League Two</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2025-12-29</t>
-        </is>
+      <c r="C10" s="2" t="n">
+        <v>46060</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AMF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="F10" t="n">
+        <v>43</v>
+      </c>
+      <c r="G10" t="n">
+        <v>17</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M10" t="n">
         <v>13</v>
       </c>
-      <c r="G10" t="n">
+      <c r="N10" t="n">
+        <v>12</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>27</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
         <v>6</v>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>5</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="AA10" t="n">
         <v>3</v>
       </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
         <v>6</v>
       </c>
-      <c r="V10" t="n">
-        <v>3</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1</v>
-      </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -12623,7 +12180,7 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -12632,64 +12189,64 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH10" t="n">
         <v>4</v>
       </c>
-      <c r="AR10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>1</v>
-      </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ10" t="n">
         <v>0</v>
@@ -12728,7 +12285,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Crawley Town - Colchester United 1:1</t>
+          <t>Crewe Alexandra - Colchester United 1:0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -12736,10 +12293,8 @@
           <t>England. League Two</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
+      <c r="C11" s="2" t="n">
+        <v>46053</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -12747,130 +12302,130 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="F11" t="n">
+        <v>41</v>
+      </c>
+      <c r="G11" t="n">
+        <v>14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="M11" t="n">
+        <v>18</v>
+      </c>
+      <c r="N11" t="n">
+        <v>9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
         <v>13</v>
       </c>
-      <c r="G11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>9</v>
-      </c>
       <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="n">
         <v>4</v>
       </c>
-      <c r="W11" t="n">
-        <v>7</v>
-      </c>
       <c r="X11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
         <v>3</v>
       </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="AG11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS11" t="n">
         <v>4</v>
       </c>
-      <c r="AA11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1</v>
-      </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
         <v>0</v>
@@ -12891,31 +12446,31 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB11" t="n">
         <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD11" t="n">
         <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
       </c>
       <c r="BH11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ11" t="n">
         <v>0</v>
@@ -12954,7 +12509,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Colchester United - Newport County 4:1</t>
+          <t>Colchester United - Grimsby Town 0:1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -12962,10 +12517,8 @@
           <t>England. League Two</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2025-12-20</t>
-        </is>
+      <c r="C12" s="2" t="n">
+        <v>46049</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -12973,175 +12526,175 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="F12" t="n">
+        <v>47</v>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>27</v>
+      </c>
+      <c r="V12" t="n">
+        <v>11</v>
+      </c>
+      <c r="W12" t="n">
+        <v>12</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>10</v>
       </c>
-      <c r="G12" t="n">
-        <v>5</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="M12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="AR12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH12" t="n">
         <v>4</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="BI12" t="n">
         <v>3</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>1</v>
       </c>
       <c r="BJ12" t="n">
         <v>0</v>
@@ -13180,7 +12733,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Salford City - Colchester United 4:3</t>
+          <t>Colchester United - Fleetwood Town 2:1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -13188,186 +12741,184 @@
           <t>England. League Two</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2025-12-13</t>
-        </is>
+      <c r="C13" s="2" t="n">
+        <v>46046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F13" t="n">
+        <v>26</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>9</v>
       </c>
-      <c r="G13" t="n">
+      <c r="N13" t="n">
+        <v>4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>13</v>
+      </c>
+      <c r="V13" t="n">
+        <v>8</v>
+      </c>
+      <c r="W13" t="n">
+        <v>4</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>97</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
         <v>3</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2</v>
-      </c>
-      <c r="N13" t="n">
-        <v>2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>6</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1</v>
-      </c>
-      <c r="W13" t="n">
+      <c r="AG13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE13" t="n">
         <v>5</v>
       </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2</v>
-      </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
       </c>
       <c r="BH13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ13" t="n">
         <v>0</v>
@@ -13406,18 +12957,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Colchester United - West Ham United U21 0:1</t>
+          <t>Colchester United - Milton Keynes Dons 1:0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>England. EFL Vertu Trophy</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2025-12-09</t>
-        </is>
+          <t>England. League Two</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>46023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -13425,31 +12974,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M14" t="n">
         <v>12</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="M14" t="n">
-        <v>8</v>
       </c>
       <c r="N14" t="n">
         <v>7</v>
@@ -13467,127 +13016,127 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V14" t="n">
+        <v>2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>4</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>5</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE14" t="n">
         <v>9</v>
       </c>
-      <c r="X14" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>7</v>
-      </c>
       <c r="BF14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BG14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BH14" t="n">
         <v>1</v>
@@ -13632,7 +13181,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colchester United - Gillingham 0:0</t>
+          <t>Gillingham - Colchester United 1:1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -13640,10 +13189,8 @@
           <t>England. League Two</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2025-12-06</t>
-        </is>
+      <c r="C15" s="2" t="n">
+        <v>46020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -13651,13 +13198,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13675,16 +13222,16 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -13693,19 +13240,19 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>6</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X15" t="n">
         <v>1</v>
@@ -13720,10 +13267,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -13732,16 +13279,16 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
@@ -13750,10 +13297,10 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
@@ -13762,19 +13309,19 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS15" t="n">
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU15" t="n">
         <v>0</v>
@@ -13789,7 +13336,7 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
@@ -13801,22 +13348,22 @@
         <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI15" t="n">
         <v>0</v>
@@ -13858,7 +13405,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Colchester United - Cheltenham Town 2:0</t>
+          <t>Crawley Town - Colchester United 1:1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -13866,10 +13413,8 @@
           <t>England. League Two</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2025-11-29</t>
-        </is>
+      <c r="C16" s="2" t="n">
+        <v>46017</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -13877,13 +13422,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13901,10 +13446,10 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -13913,10 +13458,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -13928,25 +13473,25 @@
         <v>9</v>
       </c>
       <c r="V16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC16" t="n">
         <v>2</v>
@@ -13958,16 +13503,16 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
@@ -13991,16 +13536,16 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AR16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="n">
         <v>0</v>
@@ -14009,7 +13554,7 @@
         <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
@@ -14027,25 +13572,25 @@
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BF16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BI16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ16" t="n">
         <v>0</v>
@@ -14084,7 +13629,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Notts County - Colchester United 1:3</t>
+          <t>Colchester United - Newport County 4:1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -14092,10 +13637,8 @@
           <t>England. League Two</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2025-11-22</t>
-        </is>
+      <c r="C17" s="2" t="n">
+        <v>46011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -14103,16 +13646,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -14121,16 +13664,16 @@
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -14151,13 +13694,13 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
         <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>1</v>
@@ -14166,112 +13709,112 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
         <v>4</v>
       </c>
-      <c r="AA17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>2</v>
-      </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ17" t="n">
         <v>0</v>
@@ -14310,32 +13853,30 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Colchester United - Fulham U21 2:0</t>
+          <t>Salford City - Colchester United 4:3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>England. EFL Vertu Trophy</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
+          <t>England. League Two</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>46004</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -14344,19 +13885,19 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -14380,22 +13921,22 @@
         <v>6</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
         <v>5</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -14404,13 +13945,13 @@
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -14428,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
@@ -14440,19 +13981,19 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
         <v>0</v>
@@ -14467,16 +14008,16 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
         <v>0</v>
@@ -14485,19 +14026,19 @@
         <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="BF18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ18" t="n">
         <v>0</v>
@@ -14536,53 +14077,51 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Colchester United - Bromley 0:2</t>
+          <t>Colchester United - West Ham United U21 0:1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>England. League Two</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2025-11-08</t>
-        </is>
+          <t>England. EFL Vertu Trophy</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46000</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LAMF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="F19" t="n">
+        <v>32</v>
+      </c>
+      <c r="G19" t="n">
+        <v>12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M19" t="n">
         <v>8</v>
       </c>
-      <c r="G19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2</v>
-      </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -14591,43 +14130,43 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
+        <v>20</v>
+      </c>
+      <c r="V19" t="n">
         <v>5</v>
       </c>
-      <c r="V19" t="n">
-        <v>1</v>
-      </c>
       <c r="W19" t="n">
+        <v>9</v>
+      </c>
+      <c r="X19" t="n">
         <v>3</v>
       </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
       <c r="Y19" t="n">
         <v>0</v>
       </c>
       <c r="Z19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="n">
         <v>3</v>
       </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -14636,16 +14175,16 @@
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
         <v>1</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
@@ -14657,7 +14196,7 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -14669,19 +14208,19 @@
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -14699,10 +14238,10 @@
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BC19" t="n">
         <v>0</v>
@@ -14711,13 +14250,13 @@
         <v>0</v>
       </c>
       <c r="BE19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF19" t="n">
         <v>3</v>
       </c>
-      <c r="BF19" t="n">
-        <v>0</v>
-      </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BH19" t="n">
         <v>1</v>
@@ -14762,226 +14301,1344 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Colchester United - Gillingham 0:0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>England. League Two</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>45997</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AMF</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>12</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>6</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Colchester United - Cheltenham Town 2:0</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>England. League Two</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>45990</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>22</v>
+      </c>
+      <c r="F21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>9</v>
+      </c>
+      <c r="N21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>9</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Notts County - Colchester United 1:3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>England. League Two</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>45983</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>27</v>
+      </c>
+      <c r="F22" t="n">
+        <v>12</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>7</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Colchester United - Fulham U21 2:0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>England. EFL Vertu Trophy</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>65</v>
+      </c>
+      <c r="F23" t="n">
+        <v>22</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M23" t="n">
+        <v>6</v>
+      </c>
+      <c r="N23" t="n">
+        <v>6</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>6</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>5</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Colchester United - Bromley 0:2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>England. League Two</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>45969</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LAMF</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>14</v>
+      </c>
+      <c r="F24" t="n">
+        <v>8</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>5</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Colchester United - Tranmere Rovers 1:1</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>England. League Two</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2025-08-02</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C25" s="2" t="n">
+        <v>45871</v>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E25" t="n">
         <v>98</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F25" t="n">
         <v>37</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G25" t="n">
         <v>16</v>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
         <v>0.21</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M25" t="n">
         <v>12</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
         <v>20</v>
       </c>
-      <c r="V20" t="n">
+      <c r="V25" t="n">
         <v>6</v>
       </c>
-      <c r="W20" t="n">
+      <c r="W25" t="n">
         <v>7</v>
       </c>
-      <c r="X20" t="n">
+      <c r="X25" t="n">
         <v>4</v>
       </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
         <v>5</v>
       </c>
-      <c r="AA20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH20" t="n">
+      <c r="AA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="n">
         <v>4</v>
       </c>
-      <c r="AI20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
+      <c r="AI25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>7</v>
       </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
         <v>3</v>
       </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE20" t="n">
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE25" t="n">
         <v>7</v>
       </c>
-      <c r="BF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH20" t="n">
+      <c r="BF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH25" t="n">
         <v>5</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BI25" t="n">
         <v>5</v>
       </c>
-      <c r="BJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT20" t="n">
+      <c r="BJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15621,89 +16278,12 @@
       <c r="AA2" t="n">
         <v>1</v>
       </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
         <v>11</v>
       </c>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="inlineStr"/>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="inlineStr"/>
-      <c r="BQ2" t="inlineStr"/>
-      <c r="BR2" t="inlineStr"/>
-      <c r="BS2" t="inlineStr"/>
-      <c r="BT2" t="inlineStr"/>
-      <c r="BU2" t="inlineStr"/>
-      <c r="BV2" t="inlineStr"/>
-      <c r="BW2" t="inlineStr"/>
-      <c r="BX2" t="inlineStr"/>
-      <c r="BY2" t="inlineStr"/>
-      <c r="BZ2" t="inlineStr"/>
-      <c r="CA2" t="inlineStr"/>
-      <c r="CB2" t="inlineStr"/>
-      <c r="CC2" t="inlineStr"/>
-      <c r="CD2" t="inlineStr"/>
-      <c r="CE2" t="inlineStr"/>
-      <c r="CF2" t="inlineStr"/>
-      <c r="CG2" t="inlineStr"/>
-      <c r="CH2" t="inlineStr"/>
-      <c r="CI2" t="inlineStr"/>
-      <c r="CJ2" t="inlineStr"/>
-      <c r="CK2" t="inlineStr"/>
-      <c r="CL2" t="inlineStr"/>
-      <c r="CM2" t="inlineStr"/>
-      <c r="CN2" t="inlineStr"/>
-      <c r="CO2" t="inlineStr"/>
-      <c r="CP2" t="inlineStr"/>
-      <c r="CQ2" t="inlineStr"/>
-      <c r="CR2" t="inlineStr"/>
-      <c r="CS2" t="inlineStr"/>
-      <c r="CT2" t="inlineStr"/>
-      <c r="CU2" t="inlineStr"/>
-      <c r="CV2" t="inlineStr"/>
-      <c r="CW2" t="inlineStr"/>
-      <c r="CX2" t="inlineStr"/>
-      <c r="CY2" t="inlineStr"/>
-      <c r="CZ2" t="inlineStr"/>
-      <c r="DA2" t="inlineStr"/>
-      <c r="DB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15795,89 +16375,12 @@
       <c r="AA3" t="n">
         <v>4</v>
       </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
         <v>2</v>
       </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
         <v>15</v>
       </c>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
-      <c r="BO3" t="inlineStr"/>
-      <c r="BP3" t="inlineStr"/>
-      <c r="BQ3" t="inlineStr"/>
-      <c r="BR3" t="inlineStr"/>
-      <c r="BS3" t="inlineStr"/>
-      <c r="BT3" t="inlineStr"/>
-      <c r="BU3" t="inlineStr"/>
-      <c r="BV3" t="inlineStr"/>
-      <c r="BW3" t="inlineStr"/>
-      <c r="BX3" t="inlineStr"/>
-      <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr"/>
-      <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="inlineStr"/>
-      <c r="CC3" t="inlineStr"/>
-      <c r="CD3" t="inlineStr"/>
-      <c r="CE3" t="inlineStr"/>
-      <c r="CF3" t="inlineStr"/>
-      <c r="CG3" t="inlineStr"/>
-      <c r="CH3" t="inlineStr"/>
-      <c r="CI3" t="inlineStr"/>
-      <c r="CJ3" t="inlineStr"/>
-      <c r="CK3" t="inlineStr"/>
-      <c r="CL3" t="inlineStr"/>
-      <c r="CM3" t="inlineStr"/>
-      <c r="CN3" t="inlineStr"/>
-      <c r="CO3" t="inlineStr"/>
-      <c r="CP3" t="inlineStr"/>
-      <c r="CQ3" t="inlineStr"/>
-      <c r="CR3" t="inlineStr"/>
-      <c r="CS3" t="inlineStr"/>
-      <c r="CT3" t="inlineStr"/>
-      <c r="CU3" t="inlineStr"/>
-      <c r="CV3" t="inlineStr"/>
-      <c r="CW3" t="inlineStr"/>
-      <c r="CX3" t="inlineStr"/>
-      <c r="CY3" t="inlineStr"/>
-      <c r="CZ3" t="inlineStr"/>
-      <c r="DA3" t="inlineStr"/>
-      <c r="DB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15912,108 +16415,12 @@
       <c r="H4" t="n">
         <v>1214</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
-      <c r="BW4" t="inlineStr"/>
-      <c r="BX4" t="inlineStr"/>
-      <c r="BY4" t="inlineStr"/>
-      <c r="BZ4" t="inlineStr"/>
-      <c r="CA4" t="inlineStr"/>
-      <c r="CB4" t="inlineStr"/>
-      <c r="CC4" t="inlineStr"/>
-      <c r="CD4" t="inlineStr"/>
-      <c r="CE4" t="inlineStr"/>
-      <c r="CF4" t="inlineStr"/>
-      <c r="CG4" t="inlineStr"/>
-      <c r="CH4" t="inlineStr"/>
-      <c r="CI4" t="inlineStr"/>
-      <c r="CJ4" t="inlineStr"/>
-      <c r="CK4" t="inlineStr"/>
-      <c r="CL4" t="inlineStr"/>
-      <c r="CM4" t="inlineStr"/>
-      <c r="CN4" t="inlineStr"/>
-      <c r="CO4" t="inlineStr"/>
-      <c r="CP4" t="inlineStr"/>
-      <c r="CQ4" t="inlineStr"/>
-      <c r="CR4" t="inlineStr"/>
-      <c r="CS4" t="inlineStr"/>
-      <c r="CT4" t="inlineStr"/>
-      <c r="CU4" t="inlineStr"/>
-      <c r="CV4" t="inlineStr"/>
-      <c r="CW4" t="inlineStr"/>
-      <c r="CX4" t="inlineStr"/>
-      <c r="CY4" t="inlineStr"/>
-      <c r="CZ4" t="inlineStr"/>
-      <c r="DA4" t="inlineStr"/>
-      <c r="DB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16105,89 +16512,12 @@
       <c r="AA5" t="n">
         <v>3</v>
       </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
         <v>2</v>
       </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
         <v>23</v>
       </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
-      <c r="BO5" t="inlineStr"/>
-      <c r="BP5" t="inlineStr"/>
-      <c r="BQ5" t="inlineStr"/>
-      <c r="BR5" t="inlineStr"/>
-      <c r="BS5" t="inlineStr"/>
-      <c r="BT5" t="inlineStr"/>
-      <c r="BU5" t="inlineStr"/>
-      <c r="BV5" t="inlineStr"/>
-      <c r="BW5" t="inlineStr"/>
-      <c r="BX5" t="inlineStr"/>
-      <c r="BY5" t="inlineStr"/>
-      <c r="BZ5" t="inlineStr"/>
-      <c r="CA5" t="inlineStr"/>
-      <c r="CB5" t="inlineStr"/>
-      <c r="CC5" t="inlineStr"/>
-      <c r="CD5" t="inlineStr"/>
-      <c r="CE5" t="inlineStr"/>
-      <c r="CF5" t="inlineStr"/>
-      <c r="CG5" t="inlineStr"/>
-      <c r="CH5" t="inlineStr"/>
-      <c r="CI5" t="inlineStr"/>
-      <c r="CJ5" t="inlineStr"/>
-      <c r="CK5" t="inlineStr"/>
-      <c r="CL5" t="inlineStr"/>
-      <c r="CM5" t="inlineStr"/>
-      <c r="CN5" t="inlineStr"/>
-      <c r="CO5" t="inlineStr"/>
-      <c r="CP5" t="inlineStr"/>
-      <c r="CQ5" t="inlineStr"/>
-      <c r="CR5" t="inlineStr"/>
-      <c r="CS5" t="inlineStr"/>
-      <c r="CT5" t="inlineStr"/>
-      <c r="CU5" t="inlineStr"/>
-      <c r="CV5" t="inlineStr"/>
-      <c r="CW5" t="inlineStr"/>
-      <c r="CX5" t="inlineStr"/>
-      <c r="CY5" t="inlineStr"/>
-      <c r="CZ5" t="inlineStr"/>
-      <c r="DA5" t="inlineStr"/>
-      <c r="DB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16222,37 +16552,12 @@
       <c r="H6" t="n">
         <v>1214</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>Colchester United - Barnet 4:1</t>
@@ -16563,18 +16868,12 @@
       <c r="AA7" t="n">
         <v>2</v>
       </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
         <v>10</v>
       </c>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>Cambridge United - Colchester United 1:1</t>
@@ -16885,18 +17184,12 @@
       <c r="AA8" t="n">
         <v>4</v>
       </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="n">
         <v>57</v>
       </c>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>Barrow - Colchester United 1:0</t>
@@ -17207,18 +17500,12 @@
       <c r="AA9" t="n">
         <v>4</v>
       </c>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="n">
         <v>1</v>
       </c>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="n">
         <v>44</v>
       </c>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr">
         <is>
           <t>Colchester United - Shrewsbury Town 2:0</t>
@@ -17529,18 +17816,12 @@
       <c r="AA10" t="n">
         <v>5</v>
       </c>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
         <v>1</v>
       </c>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="n">
         <v>25</v>
       </c>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr">
         <is>
           <t>Crewe Alexandra - Colchester United 1:0</t>
@@ -17851,18 +18132,12 @@
       <c r="AA11" t="n">
         <v>2</v>
       </c>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="n">
         <v>49</v>
       </c>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>Colchester United - Grimsby Town 0:1</t>
@@ -18173,18 +18448,12 @@
       <c r="AA12" t="n">
         <v>1</v>
       </c>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="n">
         <v>1</v>
       </c>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="n">
         <v>20</v>
       </c>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>Colchester United - Fleetwood Town 2:1</t>
@@ -18495,18 +18764,12 @@
       <c r="AA13" t="n">
         <v>6</v>
       </c>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="n">
         <v>3</v>
       </c>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="n">
         <v>37</v>
       </c>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>Colchester United - Milton Keynes Dons 1:0</t>
@@ -18817,18 +19080,12 @@
       <c r="AA14" t="n">
         <v>2</v>
       </c>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="n">
         <v>6</v>
       </c>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr">
         <is>
           <t>Gillingham - Colchester United 1:1</t>
@@ -19139,18 +19396,12 @@
       <c r="AA15" t="n">
         <v>3</v>
       </c>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="n">
         <v>7</v>
       </c>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr">
         <is>
           <t>Crawley Town - Colchester United 1:1</t>
@@ -19461,18 +19712,12 @@
       <c r="AA16" t="n">
         <v>0</v>
       </c>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="n">
         <v>11</v>
       </c>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr">
         <is>
           <t>Colchester United - Newport County 4:1</t>
@@ -19783,18 +20028,12 @@
       <c r="AA17" t="n">
         <v>0</v>
       </c>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="n">
         <v>0</v>
       </c>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="n">
         <v>3</v>
       </c>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr">
         <is>
           <t>Salford City - Colchester United 4:3</t>
@@ -20016,45 +20255,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>Colchester United - West Ham United U21 0:1</t>
@@ -20365,18 +20570,12 @@
       <c r="AA19" t="n">
         <v>0</v>
       </c>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="n">
         <v>0</v>
       </c>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="n">
         <v>5</v>
       </c>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr">
         <is>
           <t>Colchester United - Gillingham 0:0</t>
@@ -20687,18 +20886,12 @@
       <c r="AA20" t="n">
         <v>1</v>
       </c>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="n">
         <v>1</v>
       </c>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="n">
         <v>14</v>
       </c>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>Colchester United - Cheltenham Town 2:0</t>
@@ -21009,18 +21202,12 @@
       <c r="AA21" t="n">
         <v>0</v>
       </c>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="n">
         <v>0</v>
       </c>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="n">
         <v>22</v>
       </c>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>Notts County - Colchester United 1:3</t>
@@ -21242,45 +21429,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>2025-11-11</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>Colchester United - Fulham U21 2:0</t>
@@ -21591,18 +21744,12 @@
       <c r="AA23" t="n">
         <v>1</v>
       </c>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="n">
         <v>0</v>
       </c>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="n">
         <v>7</v>
       </c>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>Colchester United - Bromley 0:2</t>
@@ -21913,18 +22060,12 @@
       <c r="AA24" t="n">
         <v>3</v>
       </c>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="n">
         <v>0</v>
       </c>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="n">
         <v>34</v>
       </c>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr">
         <is>
           <t>Colchester United - Tranmere Rovers 1:1</t>
